--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487602_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487602_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9432</v>
+        <v>4.4158</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8373</v>
+        <v>4.1191</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1059</v>
+        <v>0.2967</v>
       </c>
       <c r="G2" t="n">
         <v>1.7431</v>
@@ -610,13 +610,13 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2001</v>
+        <v>0.6727</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0595</v>
+        <v>0.2223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2596</v>
+        <v>0.4503</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6359</v>
+        <v>2.2932</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5537</v>
+        <v>3.3746</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-1.0813</v>
       </c>
       <c r="G3" t="n">
         <v>2.0862</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2974</v>
+        <v>0.9547</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2146</v>
+        <v>1.0355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0828</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-0.9418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7611</v>
+        <v>1.4921</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8825</v>
+        <v>0.3192</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1215</v>
+        <v>1.1729</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6826</v>
+        <v>2.6877</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8193</v>
+        <v>2.9363</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1367</v>
+        <v>-0.2486</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7079</v>
+        <v>3.435</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7435</v>
+        <v>3.3944</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0356</v>
+        <v>0.0406</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0254</v>
+        <v>-0.7473</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.4581</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1011</v>
+        <v>-0.2892</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1344</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5531</v>
+        <v>0.1626</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5791</v>
+        <v>-0.2053</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.026</v>
+        <v>0.3679</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6597</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6951</v>
+        <v>1.4704</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4304</v>
+        <v>1.1511</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2648</v>
+        <v>0.3193</v>
       </c>
       <c r="G5" t="n">
         <v>-0.077</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2304</v>
+        <v>0.0056</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1828</v>
+        <v>-0.0965</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0476</v>
+        <v>0.1021</v>
       </c>
       <c r="V5" t="n">
         <v>0.3776</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4006</v>
+        <v>1.1509</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2629</v>
+        <v>2.1633</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6635</v>
+        <v>-1.0125</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6877</v>
+        <v>1.6826</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9363</v>
+        <v>2.8193</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2486</v>
+        <v>-1.1367</v>
       </c>
       <c r="J6" t="n">
-        <v>3.435</v>
+        <v>2.7079</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3944</v>
+        <v>2.7435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0406</v>
+        <v>-0.0356</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7473</v>
+        <v>-1.0254</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4581</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2892</v>
+        <v>-1.1011</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0711</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7874</v>
+        <v>0.8599</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8585</v>
+        <v>0.083</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0953</v>
+        <v>0.1034</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6124</v>
+        <v>-0.7526</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7077</v>
+        <v>0.8559</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8206</v>
+        <v>-1.9798</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9246</v>
+        <v>0.1845</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.104</v>
+        <v>-2.1644</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3392</v>
+        <v>-0.8266</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2986</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>-1.4692</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5187</v>
+        <v>-1.1533</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.374</v>
+        <v>-0.4581</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1446</v>
+        <v>-0.6952</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1577</v>
+        <v>-0.2064</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2434</v>
+        <v>0.074</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4011</v>
+        <v>-0.2804</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1761</v>
+        <v>1.3194</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1761</v>
+        <v>1.3194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0366</v>
+        <v>-0.2806</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6745</v>
+        <v>1.3727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6379</v>
+        <v>-1.6532</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9798</v>
+        <v>1.8206</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1845</v>
+        <v>1.9246</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1644</v>
+        <v>-0.104</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8266</v>
+        <v>2.3392</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6425999999999999</v>
+        <v>2.2986</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4692</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1533</v>
+        <v>-0.5187</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4581</v>
+        <v>-0.374</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6952</v>
+        <v>-0.1446</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9702</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3463</v>
+        <v>-0.3429</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8479</v>
+        <v>0.0036</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4984</v>
+        <v>-0.3465</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3194</v>
+        <v>-1.1761</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.3194</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9686</v>
+        <v>-1.6839</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1633</v>
+        <v>1.2845</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1319</v>
+        <v>-2.9684</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0871</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3755</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4845</v>
+        <v>-0.3634</v>
       </c>
       <c r="U9" t="n">
-        <v>0.109</v>
+        <v>0.2725</v>
       </c>
       <c r="V9" t="n">
         <v>-1.506</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4577</v>
+        <v>-1.9985</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6252</v>
+        <v>-1.3764</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.083</v>
+        <v>-0.6221</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1751</v>
+        <v>-0.8834</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0428</v>
+        <v>2.0457</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2179</v>
+        <v>-2.9291</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.346</v>
+        <v>0.1189</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.346</v>
+        <v>1.4129</v>
       </c>
       <c r="L10" t="n">
+        <v>-1.2941</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.0023</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6327</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.635</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.5821</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.0078</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.6597</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.6597</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.829</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3889</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.2179</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.971</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.9713000000000001</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.0002</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-2.4477</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-2.4477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5994</v>
+        <v>-2.1443</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3589</v>
+        <v>-1.3084</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2405</v>
+        <v>-0.836</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8834</v>
+        <v>-0.8499</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0457</v>
+        <v>0.3913</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9291</v>
+        <v>-1.2413</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1189</v>
+        <v>0.2253</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4129</v>
+        <v>0.9104</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2941</v>
+        <v>-0.6851</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0023</v>
+        <v>-1.0752</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6327</v>
+        <v>-0.5191</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.635</v>
+        <v>-0.5561</v>
       </c>
       <c r="P11" t="n">
         <v>-0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4742</v>
+        <v>-0.1004</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8479</v>
+        <v>-0.2053</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3737</v>
+        <v>0.1049</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6597</v>
+        <v>-0.6119</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6597</v>
+        <v>0.6119</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8021</v>
+        <v>-2.8282</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8299</v>
+        <v>0.1458</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9722</v>
+        <v>-2.974</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8499</v>
+        <v>-1.1751</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3913</v>
+        <v>0.0428</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2413</v>
+        <v>-1.2179</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2253</v>
+        <v>-0.346</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9104</v>
+        <v>-0.346</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6851</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0752</v>
+        <v>-0.829</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5191</v>
+        <v>0.3889</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5561</v>
+        <v>-1.2179</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7582</v>
+        <v>0.6006</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7268</v>
+        <v>0.4918</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0314</v>
+        <v>0.1088</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6119</v>
+        <v>-2.4477</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4762</v>
+        <v>1.9903</v>
       </c>
       <c r="E13" t="n">
-        <v>8.9786</v>
+        <v>10.4929</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.5025</v>
+        <v>-8.502700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>4.9679</v>
@@ -1453,7 +1453,7 @@
         <v>-10.3875</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5683999999999999</v>
+        <v>0.5684000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-10.9557</v>
@@ -1468,10 +1468,10 @@
         <v>8.7315</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2112</v>
+        <v>2.7254</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4371999999999997</v>
+        <v>1.9512</v>
       </c>
       <c r="U13" t="n">
         <v>0.7741</v>
@@ -1483,7 +1483,7 @@
         <v>3.8582</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.620800000000001</v>
+        <v>-7.6208</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1371</v>
+        <v>4.5187</v>
       </c>
       <c r="E14" t="n">
         <v>6.3101</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1729</v>
+        <v>-1.7914</v>
       </c>
       <c r="G14" t="n">
         <v>3.2459</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1685</v>
+        <v>0.2131</v>
       </c>
       <c r="T14" t="n">
         <v>0.2568</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4253</v>
+        <v>-0.0437</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6866</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7644</v>
+        <v>3.0191</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2274</v>
+        <v>3.4275</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4629</v>
+        <v>-0.4084</v>
       </c>
       <c r="G15" t="n">
         <v>-0.06900000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.286</v>
+        <v>-1.0313</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9085</v>
+        <v>-0.7083</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3775</v>
+        <v>-0.323</v>
       </c>
       <c r="V15" t="n">
         <v>4.8955</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3934</v>
+        <v>-0.0516</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.3728</v>
+        <v>-2.2727</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7662</v>
+        <v>2.2211</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3443</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.775</v>
+        <v>0.33</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2894</v>
+        <v>-0.1893</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0644</v>
+        <v>0.5193</v>
       </c>
       <c r="V16" t="n">
         <v>0.1865</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2055</v>
+        <v>-0.6515</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7587</v>
+        <v>1.2582</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9642</v>
+        <v>-1.9097</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1441</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.255</v>
+        <v>-0.1909</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4385</v>
+        <v>-0.062</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1835</v>
+        <v>-0.129</v>
       </c>
       <c r="V17" t="n">
         <v>0.4895</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5223</v>
+        <v>-1.341</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9597</v>
+        <v>0.3591</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.482</v>
+        <v>-1.7001</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1443</v>
@@ -1858,13 +1858,13 @@
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4921</v>
+        <v>0.6735</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9847</v>
+        <v>0.3841</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5074</v>
+        <v>0.2894</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4522</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6032</v>
+        <v>-1.5398</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6425</v>
+        <v>0.5424</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2457</v>
+        <v>-2.0822</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1882</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8133</v>
+        <v>0.8768</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5596</v>
+        <v>0.4595</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2537</v>
+        <v>0.4172</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4522</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1184</v>
+        <v>-1.7274</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4529</v>
+        <v>0.6531</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5713</v>
+        <v>-2.3805</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2088</v>
@@ -2014,13 +2014,13 @@
         <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5215</v>
+        <v>-1.1306</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6046</v>
+        <v>-0.4044</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.917</v>
+        <v>-0.7262</v>
       </c>
       <c r="V20" t="n">
         <v>0.6119</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3216</v>
+        <v>-2.7027</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4758</v>
+        <v>-1.7751</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8459</v>
+        <v>-0.9276</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1149</v>
@@ -2092,13 +2092,13 @@
         <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5709</v>
+        <v>-0.9519</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2113</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3595</v>
+        <v>-0.4413</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8299</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4760999999999989</v>
+        <v>-0.4762000000000004</v>
       </c>
       <c r="E22" t="n">
-        <v>8.502699999999999</v>
+        <v>8.502600000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.9787</v>
+        <v>-8.9788</v>
       </c>
       <c r="G22" t="n">
         <v>-4.967700000000001</v>
@@ -2170,10 +2170,10 @@
         <v>10.6719</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2115</v>
+        <v>-1.2113</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7742</v>
+        <v>-0.7742000000000001</v>
       </c>
       <c r="U22" t="n">
         <v>-0.4373</v>
